--- a/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,2</t>
+          <t>0,0; 34,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,62</t>
+          <t>0,0; 23,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,41</t>
+          <t>0,0; 47,86</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 19,52</t>
+          <t>2,14; 18,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,06</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,97</t>
+          <t>0,0; 14,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,01</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,41</t>
+          <t>1,18; 11,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,57</t>
+          <t>1,0; 8,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 8,98</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,0</t>
+          <t>0,0; 28,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,24</t>
+          <t>0,0; 36,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,69</t>
+          <t>0,0; 32,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,07</t>
+          <t>0,0; 34,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,72</t>
+          <t>0,0; 16,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 22,56</t>
+          <t>2,38; 21,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,3</t>
+          <t>0,0; 21,95</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,69</t>
+          <t>1,44; 13,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,7</t>
+          <t>2,16; 12,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,26</t>
+          <t>1,17; 13,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,39</t>
+          <t>1,1; 11,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,32</t>
+          <t>1,42; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,07</t>
+          <t>2,21; 9,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,06</t>
+          <t>1,37; 8,93</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3491</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3994</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4221</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>634; 5490</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5525</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4533</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5182</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3602</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>718; 6749</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>802; 6854</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4547</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6065</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3196</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3857</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3124</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>652; 5945</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5702</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>631; 5838</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7408</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>645; 7630</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>699; 7449</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6036</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1283; 7126</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2760; 11640</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1413; 9195</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,7</t>
+          <t>0,0; 31,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,35</t>
+          <t>0,0; 21,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,86</t>
+          <t>0,0; 44,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 18,53</t>
+          <t>2,15; 19,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,24</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 11,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,07</t>
+          <t>1,18; 11,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,53</t>
+          <t>1,02; 8,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
     </row>
@@ -903,22 +903,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,1</t>
+          <t>0,0; 28,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,26</t>
+          <t>0,0; 31,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,43</t>
+          <t>0,0; 32,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 35,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,93</t>
+          <t>0,0; 17,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 21,7</t>
+          <t>2,39; 23,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,95</t>
+          <t>0,0; 21,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,31</t>
+          <t>1,42; 13,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,09</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,84</t>
+          <t>1,15; 11,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,72</t>
+          <t>1,1; 11,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,87</t>
+          <t>1,42; 8,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,32</t>
+          <t>2,18; 8,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,93</t>
+          <t>1,65; 9,34</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3491</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3994</t>
+          <t>0; 3623</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4221</t>
+          <t>0; 3946</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>634; 5490</t>
+          <t>637; 5722</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5525</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 4220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3669</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5182</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3602</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>718; 6749</t>
+          <t>718; 6770</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>802; 6854</t>
+          <t>818; 7147</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6125</t>
+          <t>0; 5915</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6065</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3196</t>
+          <t>0; 3245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3857</t>
+          <t>0; 3986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>652; 5945</t>
+          <t>656; 6373</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5702</t>
+          <t>0; 5635</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>631; 5838</t>
+          <t>625; 5714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1321; 7408</t>
+          <t>1339; 7993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645; 7630</t>
+          <t>632; 6543</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>699; 7449</t>
+          <t>697; 7349</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1283; 7126</t>
+          <t>1285; 7474</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2760; 11640</t>
+          <t>2718; 10619</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1413; 9195</t>
+          <t>1699; 9614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,82%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,08%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 30,2</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,18</t>
+          <t>0,0; 21,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,75</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 19,31</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>0,0; 12,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,71</t>
+          <t>2,14; 19,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 13,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 12,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,1</t>
+          <t>1,2; 11,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,9</t>
+          <t>0,87; 8,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 36,69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 35,07</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,7</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,53</t>
+          <t>0,0; 25,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,24</t>
+          <t>0,0; 14,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 23,26</t>
+          <t>2,4; 22,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,7</t>
+          <t>0,0; 21,3</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,02</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,04</t>
+          <t>1,09; 10,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,87</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>1,46; 12,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,56</t>
+          <t>2,17; 12,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>1,14; 12,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,25</t>
+          <t>1,44; 9,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,51</t>
+          <t>1,87; 9,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,34</t>
+          <t>1,54; 9,06</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,27 +1205,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1258,27 +1258,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1311,42 +1311,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3038</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2239</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3623</t>
+          <t>0; 3699</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3476</t>
         </is>
       </c>
     </row>
@@ -1363,22 +1363,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2158</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1487</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>637; 5722</t>
+          <t>0; 3451</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4525</t>
+          <t>0; 4964</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4220</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3669</t>
+          <t>633; 5783</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5348</t>
+          <t>0; 4578</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4464</t>
+          <t>0; 4127</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>718; 6770</t>
+          <t>732; 6958</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>818; 7147</t>
+          <t>696; 6883</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5915</t>
+          <t>0; 5823</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1317</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1760</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 3616</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3934</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4561</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5302</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3245</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 4045</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 2717</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>656; 6373</t>
+          <t>658; 6183</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5635</t>
+          <t>0; 5533</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2158</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3517</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2531</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>625; 5714</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1339; 7993</t>
+          <t>690; 6601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>632; 6543</t>
+          <t>0; 6241</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>639; 5567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>697; 7349</t>
+          <t>1329; 7782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>627; 6756</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1285; 7474</t>
+          <t>1304; 8444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2718; 10619</t>
+          <t>2335; 11319</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1699; 9614</t>
+          <t>1581; 9329</t>
         </is>
       </c>
     </row>
